--- a/Python/results/metrics_agg.xlsx
+++ b/Python/results/metrics_agg.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdaly\Documents\MasterThese\Design_Pattern_Prototyping\Python\results\"/>
     </mc:Choice>
@@ -16,7 +16,7 @@
   </sheets>
   <calcPr calcId="162913" iterateCount="1" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="596">
   <si>
     <t>Pattern</t>
   </si>
@@ -1760,12 +1760,76 @@
   </si>
   <si>
     <t>992586.7562274145</t>
+  </si>
+  <si>
+    <t>2025-05-06 12:03:28</t>
+  </si>
+  <si>
+    <t>93.30994444444444</t>
+  </si>
+  <si>
+    <t>3409903794.825926</t>
+  </si>
+  <si>
+    <t>19261382171.396297</t>
+  </si>
+  <si>
+    <t>13808119837.292593</t>
+  </si>
+  <si>
+    <t>1.4798122450403744E8</t>
+  </si>
+  <si>
+    <t>0.7168810480173144</t>
+  </si>
+  <si>
+    <t>0.0026206368474576257</t>
+  </si>
+  <si>
+    <t>0.008241379310344831</t>
+  </si>
+  <si>
+    <t>2622350.6896551726</t>
+  </si>
+  <si>
+    <t>2025-05-06 12:22:01</t>
+  </si>
+  <si>
+    <t>95.03634444444444</t>
+  </si>
+  <si>
+    <t>3300299622.1370373</t>
+  </si>
+  <si>
+    <t>19595883446.155556</t>
+  </si>
+  <si>
+    <t>12988774710.981482</t>
+  </si>
+  <si>
+    <t>1.3667165742653698E8</t>
+  </si>
+  <si>
+    <t>0.6628318007030044</t>
+  </si>
+  <si>
+    <t>5.379495844684299</t>
+  </si>
+  <si>
+    <t>0.0026387976833333335</t>
+  </si>
+  <si>
+    <t>0.008541666666666663</t>
+  </si>
+  <si>
+    <t>2840638.6427118173</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2152,22 +2216,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="25.25390625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.5"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="17.4296875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="18.3828125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="21.5390625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="21.20703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="7" width="21.84375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="20.35546875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="18.3828125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="4" width="18.3828125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="29.09765625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="21.3828125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.3828125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -2212,88 +2276,88 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>18</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="0">
         <f t="shared" ref="H2:H65" si="0">G2/D2</f>
         <v>1.4013457563820728</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="0">
         <f t="shared" ref="I2:I9" si="1">G2/F2</f>
         <v>0.67854717190076086</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" t="s" s="0">
         <v>28</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="0">
         <f t="shared" si="0"/>
         <v>1.4922061091786343</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="0">
         <f t="shared" si="1"/>
         <v>7.198621758635773</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" t="s" s="0">
         <v>23</v>
       </c>
     </row>
@@ -2341,131 +2405,131 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" t="s" s="0">
         <v>46</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="0">
         <f t="shared" si="0"/>
         <v>1.4827311337120825</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="0">
         <f t="shared" si="1"/>
         <v>7.1812222671448032</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" t="s" s="0">
         <v>53</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="0">
         <f t="shared" si="0"/>
         <v>14917155434.025574</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="0">
         <f t="shared" si="1"/>
         <v>0.72457698024577954</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" t="s" s="0">
         <v>60</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" t="s" s="0">
         <v>61</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="0">
         <f t="shared" si="0"/>
         <v>1.4895570247823258</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="0">
         <f t="shared" si="1"/>
         <v>7.2215822087238291</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" t="s" s="0">
         <v>65</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" t="s" s="0">
         <v>23</v>
       </c>
     </row>
@@ -2513,131 +2577,131 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>73</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" t="s" s="0">
         <v>75</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" t="s" s="0">
         <v>76</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" t="s" s="0">
         <v>77</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="0">
         <f t="shared" si="0"/>
         <v>1.4895122147969291</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="0">
         <f t="shared" si="1"/>
         <v>7.1108808285746843</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M9" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>73</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" t="s" s="0">
         <v>84</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="0">
         <f t="shared" si="0"/>
         <v>1.3969863400111013</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="0">
         <f t="shared" ref="I10:I26" si="2">G10/F10</f>
         <v>0.67145819441204235</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" t="s" s="0">
         <v>86</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M10" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>73</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" t="s" s="0">
         <v>91</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="0">
         <f t="shared" si="0"/>
         <v>1.4720742749386171</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="0">
         <f t="shared" si="2"/>
         <v>7.1406652132450192</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="M11" t="s">
+      <c r="M11" t="s" s="0">
         <v>23</v>
       </c>
     </row>
@@ -2685,86 +2749,86 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" t="s" s="0">
         <v>106</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" t="s" s="0">
         <v>107</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="0">
         <f t="shared" si="0"/>
         <v>0.13803072127007246</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" t="s" s="0">
         <v>109</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" t="s" s="0">
         <v>110</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="M13" t="s">
+      <c r="M13" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" t="s" s="0">
         <v>113</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" t="s" s="0">
         <v>114</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" t="s" s="0">
         <v>115</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" t="s" s="0">
         <v>116</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="0">
         <f t="shared" si="0"/>
         <v>0.95720916654271371</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" t="s" s="0">
         <v>118</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" t="s" s="0">
         <v>119</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" t="s" s="0">
         <v>121</v>
       </c>
-      <c r="M14" t="s">
+      <c r="M14" t="s" s="0">
         <v>23</v>
       </c>
     </row>
@@ -2832,7 +2896,7 @@
       <c r="G16" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="0">
         <f t="shared" si="0"/>
         <v>1.497582573211778</v>
       </c>
@@ -2849,7 +2913,7 @@
       <c r="L16" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="M16" t="s">
+      <c r="M16" t="s" s="0">
         <v>23</v>
       </c>
     </row>
@@ -2875,7 +2939,7 @@
       <c r="G17" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="0">
         <f t="shared" si="0"/>
         <v>0.14988394922131024</v>
       </c>
@@ -2892,7 +2956,7 @@
       <c r="L17" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="M17" t="s">
+      <c r="M17" t="s" s="0">
         <v>23</v>
       </c>
     </row>
@@ -2961,7 +3025,7 @@
       <c r="G19" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="0">
         <f t="shared" si="0"/>
         <v>1.5224501426219956</v>
       </c>
@@ -2978,49 +3042,49 @@
       <c r="L19" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="M19" t="s">
+      <c r="M19" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>154</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" t="s" s="0">
         <v>163</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" t="s" s="0">
         <v>165</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" t="s" s="0">
         <v>166</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="0">
         <f t="shared" si="0"/>
         <v>14349304770.186092</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" t="s" s="0">
         <v>168</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" t="s" s="0">
         <v>169</v>
       </c>
-      <c r="L20" t="s">
+      <c r="L20" t="s" s="0">
         <v>170</v>
       </c>
-      <c r="M20" t="s">
+      <c r="M20" t="s" s="0">
         <v>23</v>
       </c>
     </row>
@@ -3088,7 +3152,7 @@
       <c r="G22" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="0">
         <f t="shared" si="0"/>
         <v>0.40281308344264677</v>
       </c>
@@ -3105,7 +3169,7 @@
       <c r="L22" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="M22" t="s">
+      <c r="M22" t="s" s="0">
         <v>23</v>
       </c>
     </row>
@@ -3174,7 +3238,7 @@
       <c r="G24" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="0">
         <f t="shared" si="0"/>
         <v>0.69539026204854082</v>
       </c>
@@ -3191,7 +3255,7 @@
       <c r="L24" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="M24" t="s">
+      <c r="M24" t="s" s="0">
         <v>23</v>
       </c>
     </row>
@@ -3325,88 +3389,88 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>225</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" t="s" s="0">
         <v>226</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" t="s" s="0">
         <v>227</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" t="s" s="0">
         <v>228</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" t="s" s="0">
         <v>229</v>
       </c>
       <c r="G28" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="0">
         <f t="shared" si="0"/>
         <v>1.2585031423117476</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="0">
         <f>G28/F28</f>
         <v>0.60523588329507938</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="K28" t="s">
+      <c r="K28" t="s" s="0">
         <v>231</v>
       </c>
-      <c r="L28" t="s">
+      <c r="L28" t="s" s="0">
         <v>232</v>
       </c>
-      <c r="M28" t="s">
+      <c r="M28" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>225</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" t="s" s="0">
         <v>233</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" t="s" s="0">
         <v>234</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" t="s" s="0">
         <v>235</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" t="s" s="0">
         <v>236</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="0">
         <f t="shared" si="0"/>
         <v>1.2529605790548759</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="0">
         <f>G29/F29</f>
         <v>0.60610226705262193</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="K29" t="s">
+      <c r="K29" t="s" s="0">
         <v>238</v>
       </c>
-      <c r="L29" t="s">
+      <c r="L29" t="s" s="0">
         <v>240</v>
       </c>
-      <c r="M29" t="s">
+      <c r="M29" t="s" s="0">
         <v>23</v>
       </c>
     </row>
@@ -3454,86 +3518,86 @@
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>130</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" t="s" s="0">
         <v>249</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" t="s" s="0">
         <v>250</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" t="s" s="0">
         <v>251</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" t="s" s="0">
         <v>252</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="0">
         <f t="shared" si="0"/>
         <v>1.4303547623622674</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" t="s" s="0">
         <v>254</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="K31" t="s">
+      <c r="K31" t="s" s="0">
         <v>255</v>
       </c>
-      <c r="L31" t="s">
+      <c r="L31" t="s" s="0">
         <v>257</v>
       </c>
-      <c r="M31" t="s">
+      <c r="M31" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>130</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" t="s" s="0">
         <v>258</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" t="s" s="0">
         <v>259</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" t="s" s="0">
         <v>260</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" t="s" s="0">
         <v>261</v>
       </c>
       <c r="G32" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="0">
         <f t="shared" si="0"/>
         <v>1.4530363999498677</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" t="s" s="0">
         <v>263</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="K32" t="s">
+      <c r="K32" t="s" s="0">
         <v>264</v>
       </c>
-      <c r="L32" t="s">
+      <c r="L32" t="s" s="0">
         <v>266</v>
       </c>
-      <c r="M32" t="s">
+      <c r="M32" t="s" s="0">
         <v>23</v>
       </c>
     </row>
@@ -3580,212 +3644,212 @@
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" t="s" s="0">
         <v>276</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" t="s" s="0">
         <v>277</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" t="s" s="0">
         <v>278</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" t="s" s="0">
         <v>279</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="0">
         <f t="shared" si="0"/>
         <v>1.4758497206278216</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I34" t="s" s="0">
         <v>281</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K34" t="s">
+      <c r="K34" t="s" s="0">
         <v>282</v>
       </c>
-      <c r="L34" t="s">
+      <c r="L34" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="M34" t="s">
+      <c r="M34" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" t="s" s="0">
         <v>283</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" t="s" s="0">
         <v>284</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" t="s" s="0">
         <v>285</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" t="s" s="0">
         <v>286</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="0">
         <f t="shared" si="0"/>
         <v>1.4803906391387429</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" t="s" s="0">
         <v>288</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K35" t="s">
+      <c r="K35" t="s" s="0">
         <v>289</v>
       </c>
-      <c r="L35" t="s">
+      <c r="L35" t="s" s="0">
         <v>290</v>
       </c>
-      <c r="M35" t="s">
+      <c r="M35" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" t="s" s="0">
         <v>291</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" t="s" s="0">
         <v>292</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" t="s" s="0">
         <v>293</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" t="s" s="0">
         <v>294</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="0">
         <f t="shared" si="0"/>
         <v>1.3905418510112031</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" t="s" s="0">
         <v>296</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="K36" t="s">
+      <c r="K36" t="s" s="0">
         <v>297</v>
       </c>
-      <c r="L36" t="s">
+      <c r="L36" t="s" s="0">
         <v>299</v>
       </c>
-      <c r="M36" t="s">
+      <c r="M36" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" t="s" s="0">
         <v>300</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" t="s" s="0">
         <v>301</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" t="s" s="0">
         <v>302</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" t="s" s="0">
         <v>303</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="0">
         <f t="shared" si="0"/>
         <v>1.4048189463801362</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" t="s" s="0">
         <v>305</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K37" t="s">
+      <c r="K37" t="s" s="0">
         <v>306</v>
       </c>
-      <c r="L37" t="s">
+      <c r="L37" t="s" s="0">
         <v>307</v>
       </c>
-      <c r="M37" t="s">
+      <c r="M37" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" t="s" s="0">
         <v>308</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" t="s" s="0">
         <v>309</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" t="s" s="0">
         <v>311</v>
       </c>
       <c r="G38" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="0">
         <f t="shared" si="0"/>
         <v>12271002363.251719</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" t="s" s="0">
         <v>313</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K38" t="s">
+      <c r="K38" t="s" s="0">
         <v>314</v>
       </c>
-      <c r="L38" t="s">
+      <c r="L38" t="s" s="0">
         <v>315</v>
       </c>
-      <c r="M38" t="s">
+      <c r="M38" t="s" s="0">
         <v>23</v>
       </c>
     </row>
@@ -3832,1179 +3896,1261 @@
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>194</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" t="s" s="0">
         <v>325</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" t="s" s="0">
         <v>326</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" t="s" s="0">
         <v>327</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" t="s" s="0">
         <v>328</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="0">
         <f t="shared" si="0"/>
         <v>7.0968589985785355</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I40" t="s" s="0">
         <v>330</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="K40" t="s">
+      <c r="K40" t="s" s="0">
         <v>331</v>
       </c>
-      <c r="L40" t="s">
+      <c r="L40" t="s" s="0">
         <v>333</v>
       </c>
-      <c r="M40" t="s">
+      <c r="M40" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>194</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" t="s" s="0">
         <v>334</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" t="s" s="0">
         <v>335</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" t="s" s="0">
         <v>336</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" t="s" s="0">
         <v>337</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="0">
         <f t="shared" si="0"/>
         <v>3.205545651985247</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I41" t="s" s="0">
         <v>339</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="K41" t="s">
+      <c r="K41" t="s" s="0">
         <v>340</v>
       </c>
-      <c r="L41" t="s">
+      <c r="L41" t="s" s="0">
         <v>342</v>
       </c>
-      <c r="M41" t="s">
+      <c r="M41" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>208</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" t="s" s="0">
         <v>343</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" t="s" s="0">
         <v>344</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" t="s" s="0">
         <v>345</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" t="s" s="0">
         <v>346</v>
       </c>
       <c r="G42" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="0">
         <f t="shared" si="0"/>
         <v>1.4913376481812619</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I42" t="s" s="0">
         <v>348</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="K42" t="s">
+      <c r="K42" t="s" s="0">
         <v>349</v>
       </c>
-      <c r="L42" t="s">
+      <c r="L42" t="s" s="0">
         <v>351</v>
       </c>
-      <c r="M42" t="s">
+      <c r="M42" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>208</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" t="s" s="0">
         <v>352</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" t="s" s="0">
         <v>353</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" t="s" s="0">
         <v>354</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" t="s" s="0">
         <v>355</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="0">
         <f t="shared" si="0"/>
         <v>1.3785131370910954E-2</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I43" t="s" s="0">
         <v>357</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K43" t="s">
+      <c r="K43" t="s" s="0">
         <v>358</v>
       </c>
-      <c r="L43" t="s">
+      <c r="L43" t="s" s="0">
         <v>359</v>
       </c>
-      <c r="M43" t="s">
+      <c r="M43" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>360</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" t="s" s="0">
         <v>361</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" t="s" s="0">
         <v>362</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" t="s" s="0">
         <v>363</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" t="s" s="0">
         <v>364</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="0">
         <f t="shared" si="0"/>
         <v>71223604008.607941</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" t="s" s="0">
         <v>366</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K44" t="s">
+      <c r="K44" t="s" s="0">
         <v>367</v>
       </c>
-      <c r="L44" t="s">
+      <c r="L44" t="s" s="0">
         <v>186</v>
       </c>
-      <c r="M44" t="s">
+      <c r="M44" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>360</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" t="s" s="0">
         <v>368</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" t="s" s="0">
         <v>369</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" t="s" s="0">
         <v>370</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" t="s" s="0">
         <v>371</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="0">
         <f t="shared" si="0"/>
         <v>3.7240177797452438</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I45" t="s" s="0">
         <v>373</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="K45" t="s">
+      <c r="K45" t="s" s="0">
         <v>374</v>
       </c>
-      <c r="L45" t="s">
+      <c r="L45" t="s" s="0">
         <v>376</v>
       </c>
-      <c r="M45" t="s">
+      <c r="M45" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" t="s" s="0">
         <v>377</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" t="s" s="0">
         <v>378</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" t="s" s="0">
         <v>379</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" t="s" s="0">
         <v>380</v>
       </c>
       <c r="G46" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="0">
         <f t="shared" si="0"/>
         <v>1.2896241092815246</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I46" t="s" s="0">
         <v>382</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K46" t="s">
+      <c r="K46" t="s" s="0">
         <v>383</v>
       </c>
-      <c r="L46" t="s">
+      <c r="L46" t="s" s="0">
         <v>384</v>
       </c>
-      <c r="M46" t="s">
+      <c r="M46" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" t="s" s="0">
         <v>385</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" t="s" s="0">
         <v>386</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" t="s" s="0">
         <v>387</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" t="s" s="0">
         <v>388</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="0">
         <f t="shared" si="0"/>
         <v>0.86784863535603762</v>
       </c>
-      <c r="I47" t="s">
+      <c r="I47" t="s" s="0">
         <v>390</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="K47" t="s">
+      <c r="K47" t="s" s="0">
         <v>391</v>
       </c>
-      <c r="L47" t="s">
+      <c r="L47" t="s" s="0">
         <v>393</v>
       </c>
-      <c r="M47" t="s">
+      <c r="M47" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" t="s" s="0">
         <v>394</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" t="s" s="0">
         <v>395</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" t="s" s="0">
         <v>396</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" t="s" s="0">
         <v>397</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="0">
         <f t="shared" si="0"/>
         <v>113723852693.68207</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" t="s" s="0">
         <v>399</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="K48" t="s">
+      <c r="K48" t="s" s="0">
         <v>400</v>
       </c>
-      <c r="L48" t="s">
+      <c r="L48" t="s" s="0">
         <v>401</v>
       </c>
-      <c r="M48" t="s">
+      <c r="M48" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" t="s" s="0">
         <v>403</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" t="s" s="0">
         <v>404</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" t="s" s="0">
         <v>405</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="0">
         <f t="shared" si="0"/>
         <v>1.3004901093286405</v>
       </c>
-      <c r="I49" t="s">
+      <c r="I49" t="s" s="0">
         <v>407</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K49" t="s">
+      <c r="K49" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="L49" t="s">
+      <c r="L49" t="s" s="0">
         <v>409</v>
       </c>
-      <c r="M49" t="s">
+      <c r="M49" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>194</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" t="s" s="0">
         <v>410</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" t="s" s="0">
         <v>411</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" t="s" s="0">
         <v>412</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" t="s" s="0">
         <v>413</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="0">
         <f t="shared" si="0"/>
         <v>1.1327618852713812</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I50" t="s" s="0">
         <v>415</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="K50" t="s">
+      <c r="K50" t="s" s="0">
         <v>416</v>
       </c>
-      <c r="L50" t="s">
+      <c r="L50" t="s" s="0">
         <v>417</v>
       </c>
-      <c r="M50" t="s">
+      <c r="M50" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="0">
         <v>194</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" t="s" s="0">
         <v>418</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" t="s" s="0">
         <v>419</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" t="s" s="0">
         <v>420</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" t="s" s="0">
         <v>421</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="0">
         <f t="shared" si="0"/>
         <v>9.9830909021578123</v>
       </c>
-      <c r="I51" t="s">
+      <c r="I51" t="s" s="0">
         <v>423</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="K51" t="s">
+      <c r="K51" t="s" s="0">
         <v>424</v>
       </c>
-      <c r="L51" t="s">
+      <c r="L51" t="s" s="0">
         <v>426</v>
       </c>
-      <c r="M51" t="s">
+      <c r="M51" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="0">
         <v>194</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" t="s" s="0">
         <v>427</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" t="s" s="0">
         <v>428</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" t="s" s="0">
         <v>429</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" t="s" s="0">
         <v>430</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="0">
         <f t="shared" si="0"/>
         <v>0.81411157994945871</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I52" t="s" s="0">
         <v>432</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="K52" t="s">
+      <c r="K52" t="s" s="0">
         <v>433</v>
       </c>
-      <c r="L52" t="s">
+      <c r="L52" t="s" s="0">
         <v>435</v>
       </c>
-      <c r="M52" t="s">
+      <c r="M52" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="A53" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" t="s" s="0">
         <v>436</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" t="s" s="0">
         <v>437</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" t="s" s="0">
         <v>438</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" t="s" s="0">
         <v>439</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="0">
         <f t="shared" si="0"/>
         <v>0.76636338824227068</v>
       </c>
-      <c r="I53" t="s">
+      <c r="I53" t="s" s="0">
         <v>441</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="K53" t="s">
+      <c r="K53" t="s" s="0">
         <v>442</v>
       </c>
-      <c r="L53" t="s">
+      <c r="L53" t="s" s="0">
         <v>444</v>
       </c>
-      <c r="M53" t="s">
+      <c r="M53" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="A54" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" t="s" s="0">
         <v>445</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" t="s" s="0">
         <v>446</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" t="s" s="0">
         <v>447</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" t="s" s="0">
         <v>448</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="0">
         <f t="shared" si="0"/>
         <v>1.5253627225372559</v>
       </c>
-      <c r="I54" t="s">
+      <c r="I54" t="s" s="0">
         <v>450</v>
       </c>
       <c r="J54" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="K54" t="s">
+      <c r="K54" t="s" s="0">
         <v>451</v>
       </c>
-      <c r="L54" t="s">
+      <c r="L54" t="s" s="0">
         <v>452</v>
       </c>
-      <c r="M54" t="s">
+      <c r="M54" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="A55" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" t="s" s="0">
         <v>453</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" t="s" s="0">
         <v>454</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" t="s" s="0">
         <v>455</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" t="s" s="0">
         <v>456</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="0">
         <f t="shared" si="0"/>
         <v>1.4060472774622863</v>
       </c>
-      <c r="I55" t="s">
+      <c r="I55" t="s" s="0">
         <v>458</v>
       </c>
       <c r="J55" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="K55" t="s">
+      <c r="K55" t="s" s="0">
         <v>459</v>
       </c>
-      <c r="L55" t="s">
+      <c r="L55" t="s" s="0">
         <v>461</v>
       </c>
-      <c r="M55" t="s">
+      <c r="M55" t="s" s="0">
         <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="A56" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" t="s" s="0">
         <v>462</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" t="s" s="0">
         <v>463</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" t="s" s="0">
         <v>464</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F56" t="s" s="0">
         <v>465</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="0">
         <f t="shared" si="0"/>
         <v>1.5115744551764858</v>
       </c>
-      <c r="I56" t="s">
+      <c r="I56" t="s" s="0">
         <v>467</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K56" t="s">
+      <c r="K56" t="s" s="0">
         <v>468</v>
       </c>
-      <c r="L56" t="s">
+      <c r="L56" t="s" s="0">
         <v>469</v>
       </c>
-      <c r="M56" t="s">
+      <c r="M56" t="s" s="0">
         <v>470</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="A57" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" t="s" s="0">
         <v>471</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" t="s" s="0">
         <v>472</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" t="s" s="0">
         <v>473</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F57" t="s" s="0">
         <v>474</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="0">
         <f t="shared" si="0"/>
         <v>1.3919709552118376</v>
       </c>
-      <c r="I57" t="s">
+      <c r="I57" t="s" s="0">
         <v>476</v>
       </c>
       <c r="J57" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="K57" t="s">
+      <c r="K57" t="s" s="0">
         <v>477</v>
       </c>
-      <c r="L57" t="s">
+      <c r="L57" t="s" s="0">
         <v>478</v>
       </c>
-      <c r="M57" t="s">
+      <c r="M57" t="s" s="0">
         <v>479</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="A58" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" t="s" s="0">
         <v>480</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" t="s" s="0">
         <v>481</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" t="s" s="0">
         <v>482</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" t="s" s="0">
         <v>483</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="0">
         <f t="shared" si="0"/>
         <v>0.52384814586598982</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I58" t="s" s="0">
         <v>485</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="K58" t="s">
+      <c r="K58" t="s" s="0">
         <v>486</v>
       </c>
-      <c r="L58" t="s">
+      <c r="L58" t="s" s="0">
         <v>487</v>
       </c>
-      <c r="M58" t="s">
+      <c r="M58" t="s" s="0">
         <v>488</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="A59" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" t="s" s="0">
         <v>489</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" t="s" s="0">
         <v>490</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" t="s" s="0">
         <v>491</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F59" t="s" s="0">
         <v>492</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="0">
         <f t="shared" si="0"/>
         <v>0.14296390383058696</v>
       </c>
-      <c r="I59" t="s">
+      <c r="I59" t="s" s="0">
         <v>494</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="K59" t="s">
+      <c r="K59" t="s" s="0">
         <v>495</v>
       </c>
-      <c r="L59" t="s">
+      <c r="L59" t="s" s="0">
         <v>497</v>
       </c>
-      <c r="M59" t="s">
+      <c r="M59" t="s" s="0">
         <v>498</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="A60" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" t="s" s="0">
         <v>499</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" t="s" s="0">
         <v>500</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" t="s" s="0">
         <v>501</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" t="s" s="0">
         <v>502</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>503</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="0">
         <f t="shared" si="0"/>
         <v>0.6954665572936215</v>
       </c>
-      <c r="I60" t="s">
+      <c r="I60" t="s" s="0">
         <v>504</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K60" t="s">
+      <c r="K60" t="s" s="0">
         <v>505</v>
       </c>
-      <c r="L60" t="s">
+      <c r="L60" t="s" s="0">
         <v>307</v>
       </c>
-      <c r="M60" t="s">
+      <c r="M60" t="s" s="0">
         <v>506</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="A61" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" t="s" s="0">
         <v>507</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" t="s" s="0">
         <v>508</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" t="s" s="0">
         <v>509</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" t="s" s="0">
         <v>510</v>
       </c>
       <c r="G61" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="0">
         <f t="shared" si="0"/>
         <v>5.0208431229218151</v>
       </c>
-      <c r="I61" t="s">
+      <c r="I61" t="s" s="0">
         <v>512</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="K61" t="s">
+      <c r="K61" t="s" s="0">
         <v>513</v>
       </c>
-      <c r="L61" t="s">
+      <c r="L61" t="s" s="0">
         <v>515</v>
       </c>
-      <c r="M61" t="s">
+      <c r="M61" t="s" s="0">
         <v>516</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="A62" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" t="s" s="0">
         <v>517</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" t="s" s="0">
         <v>518</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" t="s" s="0">
         <v>519</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F62" t="s" s="0">
         <v>520</v>
       </c>
       <c r="G62" s="7" t="s">
         <v>521</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="0">
         <f t="shared" si="0"/>
         <v>0.37660719360152212</v>
       </c>
-      <c r="I62" t="s">
+      <c r="I62" t="s" s="0">
         <v>522</v>
       </c>
       <c r="J62" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="K62" t="s">
+      <c r="K62" t="s" s="0">
         <v>523</v>
       </c>
-      <c r="L62" t="s">
+      <c r="L62" t="s" s="0">
         <v>525</v>
       </c>
-      <c r="M62" t="s">
+      <c r="M62" t="s" s="0">
         <v>526</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="A63" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" t="s" s="0">
         <v>527</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" t="s" s="0">
         <v>528</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" t="s" s="0">
         <v>529</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" t="s" s="0">
         <v>530</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="0">
         <f t="shared" si="0"/>
         <v>0.11336342886490665</v>
       </c>
-      <c r="I63" t="s">
+      <c r="I63" t="s" s="0">
         <v>532</v>
       </c>
       <c r="J63" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="K63" t="s">
+      <c r="K63" t="s" s="0">
         <v>533</v>
       </c>
-      <c r="L63" t="s">
+      <c r="L63" t="s" s="0">
         <v>535</v>
       </c>
-      <c r="M63" t="s">
+      <c r="M63" t="s" s="0">
         <v>536</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="A64" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" t="s" s="0">
         <v>537</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" t="s" s="0">
         <v>538</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" t="s" s="0">
         <v>539</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F64" t="s" s="0">
         <v>540</v>
       </c>
       <c r="G64" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="H64">
+      <c r="H64" s="0">
         <f t="shared" si="0"/>
         <v>1.2410422298676185</v>
       </c>
-      <c r="I64" t="s">
+      <c r="I64" t="s" s="0">
         <v>542</v>
       </c>
       <c r="J64" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="K64" t="s">
+      <c r="K64" t="s" s="0">
         <v>543</v>
       </c>
-      <c r="L64" t="s">
+      <c r="L64" t="s" s="0">
         <v>545</v>
       </c>
-      <c r="M64" t="s">
+      <c r="M64" t="s" s="0">
         <v>546</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="A65" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" t="s" s="0">
         <v>547</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" t="s" s="0">
         <v>548</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65" t="s" s="0">
         <v>549</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F65" t="s" s="0">
         <v>550</v>
       </c>
       <c r="G65" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="H65">
+      <c r="H65" s="0">
         <f t="shared" si="0"/>
         <v>11.944208040375226</v>
       </c>
-      <c r="I65" t="s">
+      <c r="I65" t="s" s="0">
         <v>552</v>
       </c>
       <c r="J65" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K65" t="s">
+      <c r="K65" t="s" s="0">
         <v>553</v>
       </c>
-      <c r="L65" t="s">
+      <c r="L65" t="s" s="0">
         <v>554</v>
       </c>
-      <c r="M65" t="s">
+      <c r="M65" t="s" s="0">
         <v>555</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+      <c r="A66" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" t="s" s="0">
         <v>556</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" t="s" s="0">
         <v>557</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" t="s" s="0">
         <v>558</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F66" t="s" s="0">
         <v>559</v>
       </c>
       <c r="G66" s="7" t="s">
         <v>560</v>
       </c>
-      <c r="H66">
+      <c r="H66" s="0">
         <f t="shared" ref="H66:H67" si="3">G66/D66</f>
         <v>8.1767786551383104</v>
       </c>
-      <c r="I66" t="s">
+      <c r="I66" t="s" s="0">
         <v>561</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K66" t="s">
+      <c r="K66" t="s" s="0">
         <v>562</v>
       </c>
-      <c r="L66" t="s">
+      <c r="L66" t="s" s="0">
         <v>563</v>
       </c>
-      <c r="M66" t="s">
+      <c r="M66" t="s" s="0">
         <v>564</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="A67" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" t="s" s="0">
         <v>565</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" t="s" s="0">
         <v>566</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" t="s" s="0">
         <v>567</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F67" t="s" s="0">
         <v>568</v>
       </c>
       <c r="G67" s="7" t="s">
         <v>569</v>
       </c>
-      <c r="H67">
+      <c r="H67" s="0">
         <f t="shared" si="3"/>
         <v>0.73007254775725317</v>
       </c>
-      <c r="I67" t="s">
+      <c r="I67" t="s" s="0">
         <v>570</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="K67" t="s">
+      <c r="K67" t="s" s="0">
         <v>571</v>
       </c>
-      <c r="L67" t="s">
+      <c r="L67" t="s" s="0">
         <v>573</v>
       </c>
-      <c r="M67" t="s">
+      <c r="M67" t="s" s="0">
         <v>574</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>360</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>575</v>
+      </c>
+      <c r="D68" t="s" s="0">
+        <v>576</v>
+      </c>
+      <c r="E68" t="s" s="0">
+        <v>577</v>
+      </c>
+      <c r="F68" t="s" s="0">
+        <v>578</v>
+      </c>
+      <c r="G68" t="s" s="7">
+        <v>579</v>
+      </c>
+      <c r="H68" t="s" s="0">
+        <v>580</v>
+      </c>
+      <c r="I68" t="s" s="0">
+        <v>581</v>
+      </c>
+      <c r="J68" t="s" s="4">
+        <v>247</v>
+      </c>
+      <c r="K68" t="s" s="0">
+        <v>582</v>
+      </c>
+      <c r="L68" t="s" s="0">
+        <v>583</v>
+      </c>
+      <c r="M68" t="s" s="0">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>360</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C69" t="s" s="0">
+        <v>585</v>
+      </c>
+      <c r="D69" t="s" s="0">
+        <v>586</v>
+      </c>
+      <c r="E69" t="s" s="0">
+        <v>587</v>
+      </c>
+      <c r="F69" t="s" s="0">
+        <v>588</v>
+      </c>
+      <c r="G69" t="s" s="7">
+        <v>589</v>
+      </c>
+      <c r="H69" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="I69" t="s" s="0">
+        <v>591</v>
+      </c>
+      <c r="J69" t="s" s="4">
+        <v>592</v>
+      </c>
+      <c r="K69" t="s" s="0">
+        <v>593</v>
+      </c>
+      <c r="L69" t="s" s="0">
+        <v>594</v>
+      </c>
+      <c r="M69" t="s" s="0">
+        <v>595</v>
       </c>
     </row>
   </sheetData>
